--- a/Result/profitability/1563.xlsx
+++ b/Result/profitability/1563.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM45"/>
+  <dimension ref="A1:AM46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.14</v>
       </c>
       <c r="M2" t="n">
-        <v>0.44625</v>
+        <v>0.38875</v>
       </c>
       <c r="N2" t="n">
-        <v>22.56875</v>
+        <v>22.3675</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-3.12</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.04249999999999998</v>
+        <v>-0.08499999999999996</v>
       </c>
       <c r="N3" t="n">
-        <v>17.15875</v>
+        <v>16.74875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.71</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.215</v>
+        <v>-0.365</v>
       </c>
       <c r="N4" t="n">
-        <v>15.1025</v>
+        <v>14.59</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>1.11</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2675</v>
+        <v>-0.19</v>
       </c>
       <c r="N5" t="n">
-        <v>14.88125</v>
+        <v>15.44625</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.67</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1475</v>
+        <v>-0.13</v>
       </c>
       <c r="N6" t="n">
-        <v>15.62125</v>
+        <v>16.4675</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.15</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1525</v>
+        <v>-0.10375</v>
       </c>
       <c r="N7" t="n">
-        <v>15.7225</v>
+        <v>16.47375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -6143,6 +6143,133 @@
       </c>
       <c r="AM45" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>1563</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>1980</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1498</v>
+      </c>
+      <c r="E46" t="n">
+        <v>482</v>
+      </c>
+      <c r="F46" t="n">
+        <v>24.32</v>
+      </c>
+      <c r="G46" t="n">
+        <v>195</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>9.83%</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>-106</v>
+      </c>
+      <c r="J46" t="n">
+        <v>88</v>
+      </c>
+      <c r="K46" t="n">
+        <v>71</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="N46" t="n">
+        <v>22.9925</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W46" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="X46" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>2.309999999999999</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0.104952294411631</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>-2.137931034482759</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0.2282828282828282</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK46" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
